--- a/src/test/resources/LoginList.xlsx
+++ b/src/test/resources/LoginList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ihsan\IdeaProjects\EuroTech_Batch8_Selenium_TestNG\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ihsan\IdeaProjects\ET_Batch19_Selenium_TestNG\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1464E4A5-53E4-4DCB-B22A-7F92F8474D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253786F4-0AB1-4111-A403-51C143A4E677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="102">
   <si>
     <t>Your Name</t>
   </si>
@@ -325,6 +325,15 @@
   </si>
   <si>
     <t>school</t>
+  </si>
+  <si>
+    <t>Tülay</t>
+  </si>
+  <si>
+    <t>Gaziantep</t>
+  </si>
+  <si>
+    <t>AEG</t>
   </si>
 </sst>
 </file>
@@ -415,7 +424,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -694,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5241B906-87AB-4B90-99C3-BB6B40C54127}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -905,6 +914,23 @@
       </c>
       <c r="E12" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
